--- a/주간행사계획_20261019_20261025.xlsx
+++ b/주간행사계획_20261019_20261025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_업무활용_프로젝트\01_진행중\02_스마트교통국\07_주간행사\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73BD8E3-E06E-4656-B1F4-DFBE24FDBD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C33B011-0C83-450A-BB10-F669C8DC3C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-6840" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{DAD55E30-93E6-4B85-BCA4-B1CD16C9CDC4}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
   <si>
     <t>(시장, 부시장) 주간행사계획</t>
   </si>
@@ -265,31 +265,36 @@
     <t>정책기획과</t>
   </si>
   <si>
+    <t>퇴계원읍</t>
+  </si>
+  <si>
+    <t>주차관리과</t>
+  </si>
+  <si>
+    <t>주차시설팀</t>
+  </si>
+  <si>
+    <t>22(목)</t>
+  </si>
+  <si>
+    <t>23(금)</t>
+  </si>
+  <si>
+    <t>24(토)</t>
+  </si>
+  <si>
+    <t>25(일)</t>
+  </si>
+  <si>
+    <t>교통국장 주간행사계획</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>시민온발걸음 현장점검(퇴계원중 주차장)</t>
-  </si>
-  <si>
-    <t>퇴계원읍</t>
-  </si>
-  <si>
-    <t>주차관리과</t>
-  </si>
-  <si>
-    <t>주차시설팀</t>
-  </si>
-  <si>
-    <t>22(목)</t>
-  </si>
-  <si>
-    <t>23(금)</t>
-  </si>
-  <si>
-    <t>24(토)</t>
-  </si>
-  <si>
-    <t>25(일)</t>
-  </si>
-  <si>
-    <t>교통국장 주간행사계획</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -926,11 +931,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1315,14 +1320,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -1354,7 +1359,7 @@
       <c r="B4" s="2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C4" s="8"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1372,7 +1377,7 @@
       <c r="B5" s="2">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C5" s="8"/>
+      <c r="C5" s="7"/>
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1408,7 +1413,7 @@
       <c r="B7" s="2">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C7" s="8"/>
+      <c r="C7" s="7"/>
       <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
@@ -1801,14 +1806,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -1930,19 +1935,19 @@
         <v>0.375</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>69</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1950,10 +1955,14 @@
         <v>64</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -1964,7 +1973,7 @@
         <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="5"/>
@@ -1978,7 +1987,7 @@
         <v>64</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="5"/>
@@ -1992,7 +2001,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="5"/>
